--- a/2-multi-document-abbyy-vs-tiled3x2+docparse-paddleocr-paddlevl/test-results/page-level-excels/oocihm.22250/oocihm.22250.169.xlsx
+++ b/2-multi-document-abbyy-vs-tiled3x2+docparse-paddleocr-paddlevl/test-results/page-level-excels/oocihm.22250/oocihm.22250.169.xlsx
@@ -464,12 +464,12 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>duplicate/tile overlap - paddle</t>
+          <t>Possible duplicate lines - paddle</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>duplicate/tile overlap - abbyy</t>
+          <t>Possible duplicate lines - abbyy</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
@@ -883,7 +883,7 @@
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>duplicate/tile overlap issue count</t>
+          <t>Possible duplicate lines issue count</t>
         </is>
       </c>
       <c r="B7" s="1" t="inlineStr">

--- a/2-multi-document-abbyy-vs-tiled3x2+docparse-paddleocr-paddlevl/test-results/page-level-excels/oocihm.22250/oocihm.22250.169.xlsx
+++ b/2-multi-document-abbyy-vs-tiled3x2+docparse-paddleocr-paddlevl/test-results/page-level-excels/oocihm.22250/oocihm.22250.169.xlsx
@@ -416,14 +416,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y31"/>
+  <dimension ref="A1:Y37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="39" customWidth="1" min="1" max="1"/>
     <col width="60" customWidth="1" min="2" max="2"/>
     <col width="60" customWidth="1" min="3" max="3"/>
-    <col width="33" customWidth="1" min="4" max="4"/>
-    <col width="32" customWidth="1" min="5" max="5"/>
+    <col width="35" customWidth="1" min="4" max="4"/>
+    <col width="34" customWidth="1" min="5" max="5"/>
     <col width="36" customWidth="1" min="6" max="6"/>
     <col width="35" customWidth="1" min="7" max="7"/>
     <col width="60" customWidth="1" min="8" max="8"/>
@@ -431,13 +431,13 @@
     <col width="60" customWidth="1" min="10" max="10"/>
     <col width="60" customWidth="1" min="11" max="11"/>
     <col width="32" customWidth="1" min="12" max="12"/>
-    <col width="31" customWidth="1" min="13" max="13"/>
+    <col width="60" customWidth="1" min="13" max="13"/>
     <col width="60" customWidth="1" min="14" max="14"/>
     <col width="60" customWidth="1" min="15" max="15"/>
     <col width="60" customWidth="1" min="16" max="16"/>
     <col width="60" customWidth="1" min="17" max="17"/>
     <col width="30" customWidth="1" min="18" max="18"/>
-    <col width="29" customWidth="1" min="19" max="19"/>
+    <col width="60" customWidth="1" min="19" max="19"/>
     <col width="30" customWidth="1" min="20" max="20"/>
     <col width="29" customWidth="1" min="21" max="21"/>
     <col width="31" customWidth="1" min="22" max="22"/>
@@ -601,16 +601,20 @@
       <c r="I2" s="1" t="inlineStr"/>
       <c r="J2" s="1" t="inlineStr">
         <is>
-          <t>L27: stray/suspicious non-ASCII glyph(s): U+00B8 CEDILLA :: ä¸Š</t>
+          <t>L27: stray/suspicious non-ASCII glyph(s): U+4E0A CJK UNIFIED IDEOGRAPH-4E0A | isolated marker/symbol line :: 上</t>
         </is>
       </c>
       <c r="K2" s="1" t="inlineStr">
         <is>
-          <t>L41: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN :: â€¢ 54 to 60</t>
+          <t>L1: BOM/control character at start of file | stray/suspicious non-ASCII glyph(s): U+FEFF ZERO WIDTH NO-BREAK SPACE | symbol-only separator/garbage line :: [BOM]162</t>
         </is>
       </c>
       <c r="L2" s="1" t="inlineStr"/>
-      <c r="M2" s="1" t="inlineStr"/>
+      <c r="M2" s="1" t="inlineStr">
+        <is>
+          <t>L1: BOM/control character at start of file | stray/suspicious non-ASCII glyph(s): U+FEFF ZERO WIDTH NO-BREAK SPACE | symbol-only separator/garbage line :: [BOM]162</t>
+        </is>
+      </c>
       <c r="N2" s="1" t="inlineStr">
         <is>
           <t>L5: isolated marker/symbol line :: 1.</t>
@@ -618,7 +622,7 @@
       </c>
       <c r="O2" s="1" t="inlineStr">
         <is>
-          <t>L34: isolated marker/symbol line :: C</t>
+          <t>L1: BOM/control character at start of file | stray/suspicious non-ASCII glyph(s): U+FEFF ZERO WIDTH NO-BREAK SPACE | symbol-only separator/garbage line :: [BOM]162</t>
         </is>
       </c>
       <c r="P2" s="1" t="inlineStr">
@@ -632,7 +636,11 @@
         </is>
       </c>
       <c r="R2" s="1" t="inlineStr"/>
-      <c r="S2" s="1" t="inlineStr"/>
+      <c r="S2" s="1" t="inlineStr">
+        <is>
+          <t>L41: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | line starts with punctuation glued to text :: • 54 to 60</t>
+        </is>
+      </c>
       <c r="T2" s="1" t="inlineStr"/>
       <c r="U2" s="1" t="inlineStr"/>
       <c r="V2" s="1" t="inlineStr"/>
@@ -653,7 +661,7 @@
       </c>
       <c r="C3" s="1" t="inlineStr">
         <is>
-          <t>151</t>
+          <t>84</t>
         </is>
       </c>
       <c r="D3" s="1" t="inlineStr"/>
@@ -668,12 +676,12 @@
       <c r="I3" s="1" t="inlineStr"/>
       <c r="J3" s="1" t="inlineStr">
         <is>
-          <t>L46: stray/suspicious non-ASCII glyph(s): U+00B8 CEDILLA, U+20AC EURO SIGN | isolated marker/symbol line :: ä¸€</t>
+          <t>L46: stray/suspicious non-ASCII glyph(s): U+4E00 CJK UNIFIED IDEOGRAPH-4E00 | isolated marker/symbol line :: 一</t>
         </is>
       </c>
       <c r="K3" s="1" t="inlineStr">
         <is>
-          <t>L51: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN :: â€¢ 54 to 64</t>
+          <t>L41: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | line starts with punctuation glued to text :: • 54 to 60</t>
         </is>
       </c>
       <c r="L3" s="1" t="inlineStr"/>
@@ -685,7 +693,7 @@
       </c>
       <c r="O3" s="1" t="inlineStr">
         <is>
-          <t>L36: isolated marker/symbol line :: I</t>
+          <t>L34: isolated marker/symbol line :: C</t>
         </is>
       </c>
       <c r="P3" s="1" t="inlineStr"/>
@@ -695,7 +703,11 @@
         </is>
       </c>
       <c r="R3" s="1" t="inlineStr"/>
-      <c r="S3" s="1" t="inlineStr"/>
+      <c r="S3" s="1" t="inlineStr">
+        <is>
+          <t>L51: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | line starts with punctuation glued to text :: • 54 to 64</t>
+        </is>
+      </c>
       <c r="T3" s="1" t="inlineStr"/>
       <c r="U3" s="1" t="inlineStr"/>
       <c r="V3" s="1" t="inlineStr"/>
@@ -731,12 +743,12 @@
       <c r="I4" s="1" t="inlineStr"/>
       <c r="J4" s="1" t="inlineStr">
         <is>
-          <t>L50: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: 54 â€” 55</t>
+          <t>L57: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | isolated marker/symbol line :: •</t>
         </is>
       </c>
       <c r="K4" s="1" t="inlineStr">
         <is>
-          <t>L55: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: 54â€”55</t>
+          <t>L51: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | line starts with punctuation glued to text :: • 54 to 64</t>
         </is>
       </c>
       <c r="L4" s="1" t="inlineStr"/>
@@ -748,7 +760,7 @@
       </c>
       <c r="O4" s="1" t="inlineStr">
         <is>
-          <t>L37: isolated marker/symbol line :: I</t>
+          <t>L36: isolated marker/symbol line :: I</t>
         </is>
       </c>
       <c r="P4" s="1" t="inlineStr"/>
@@ -774,7 +786,7 @@
       </c>
       <c r="B5" s="1" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>36</t>
         </is>
       </c>
       <c r="C5" s="1" t="inlineStr">
@@ -790,12 +802,12 @@
       <c r="I5" s="1" t="inlineStr"/>
       <c r="J5" s="1" t="inlineStr">
         <is>
-          <t>L57: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN | isolated marker/symbol line :: â€¢</t>
+          <t>L58: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | isolated marker/symbol line :: •</t>
         </is>
       </c>
       <c r="K5" s="1" t="inlineStr">
         <is>
-          <t>L57: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: 55â€”56â€”57</t>
+          <t>L59: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | isolated marker/symbol line :: •</t>
         </is>
       </c>
       <c r="L5" s="1" t="inlineStr"/>
@@ -807,7 +819,7 @@
       </c>
       <c r="O5" s="1" t="inlineStr">
         <is>
-          <t>L38: isolated marker/symbol line :: i</t>
+          <t>L37: isolated marker/symbol line :: I</t>
         </is>
       </c>
       <c r="P5" s="1" t="inlineStr"/>
@@ -847,14 +859,10 @@
       <c r="G6" s="1" t="inlineStr"/>
       <c r="H6" s="1" t="inlineStr"/>
       <c r="I6" s="1" t="inlineStr"/>
-      <c r="J6" s="1" t="inlineStr">
-        <is>
-          <t>L58: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN | isolated marker/symbol line :: â€¢</t>
-        </is>
-      </c>
+      <c r="J6" s="1" t="inlineStr"/>
       <c r="K6" s="1" t="inlineStr">
         <is>
-          <t>L59: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN | isolated marker/symbol line :: â€¢</t>
+          <t>L98: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | isolated marker/symbol line :: •</t>
         </is>
       </c>
       <c r="L6" s="1" t="inlineStr"/>
@@ -866,7 +874,7 @@
       </c>
       <c r="O6" s="1" t="inlineStr">
         <is>
-          <t>L39: isolated marker/symbol line :: J</t>
+          <t>L38: isolated marker/symbol line :: i</t>
         </is>
       </c>
       <c r="P6" s="1" t="inlineStr"/>
@@ -902,14 +910,10 @@
       <c r="G7" s="1" t="inlineStr"/>
       <c r="H7" s="1" t="inlineStr"/>
       <c r="I7" s="1" t="inlineStr"/>
-      <c r="J7" s="1" t="inlineStr">
-        <is>
-          <t>L62: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: 58 â€” 59</t>
-        </is>
-      </c>
+      <c r="J7" s="1" t="inlineStr"/>
       <c r="K7" s="1" t="inlineStr">
         <is>
-          <t>L65: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: 57â€”58</t>
+          <t>L102: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | isolated marker/symbol line :: •</t>
         </is>
       </c>
       <c r="L7" s="1" t="inlineStr"/>
@@ -921,7 +925,7 @@
       </c>
       <c r="O7" s="1" t="inlineStr">
         <is>
-          <t>L43: isolated marker/symbol line :: 54</t>
+          <t>L39: isolated marker/symbol line :: J</t>
         </is>
       </c>
       <c r="P7" s="1" t="inlineStr"/>
@@ -957,14 +961,10 @@
       <c r="G8" s="1" t="inlineStr"/>
       <c r="H8" s="1" t="inlineStr"/>
       <c r="I8" s="1" t="inlineStr"/>
-      <c r="J8" s="1" t="inlineStr">
-        <is>
-          <t>L86: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: 107 â€” 108</t>
-        </is>
-      </c>
+      <c r="J8" s="1" t="inlineStr"/>
       <c r="K8" s="1" t="inlineStr">
         <is>
-          <t>L73: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: 58â€”59</t>
+          <t>L104: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | isolated marker/symbol line :: •</t>
         </is>
       </c>
       <c r="L8" s="1" t="inlineStr"/>
@@ -976,7 +976,7 @@
       </c>
       <c r="O8" s="1" t="inlineStr">
         <is>
-          <t>L45: isolated marker/symbol line :: 64</t>
+          <t>L43: isolated marker/symbol line :: 54</t>
         </is>
       </c>
       <c r="P8" s="1" t="inlineStr"/>
@@ -1012,14 +1012,10 @@
       <c r="G9" s="1" t="inlineStr"/>
       <c r="H9" s="1" t="inlineStr"/>
       <c r="I9" s="1" t="inlineStr"/>
-      <c r="J9" s="1" t="inlineStr">
-        <is>
-          <t>L91: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: diction of the Court of Chancery 8 â€” 9</t>
-        </is>
-      </c>
+      <c r="J9" s="1" t="inlineStr"/>
       <c r="K9" s="1" t="inlineStr">
         <is>
-          <t>L98: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN | isolated marker/symbol line :: â€¢</t>
+          <t>L105: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | isolated marker/symbol line :: •</t>
         </is>
       </c>
       <c r="L9" s="1" t="inlineStr"/>
@@ -1031,7 +1027,7 @@
       </c>
       <c r="O9" s="1" t="inlineStr">
         <is>
-          <t>L47: isolated marker/symbol line :: 54</t>
+          <t>L45: isolated marker/symbol line :: 64</t>
         </is>
       </c>
       <c r="P9" s="1" t="inlineStr"/>
@@ -1053,12 +1049,12 @@
       </c>
       <c r="B10" s="1" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>4</t>
         </is>
       </c>
       <c r="C10" s="1" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>13</t>
         </is>
       </c>
       <c r="D10" s="1" t="inlineStr"/>
@@ -1070,7 +1066,7 @@
       <c r="J10" s="1" t="inlineStr"/>
       <c r="K10" s="1" t="inlineStr">
         <is>
-          <t>L102: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN | isolated marker/symbol line :: â€¢</t>
+          <t>L106: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | isolated marker/symbol line :: •</t>
         </is>
       </c>
       <c r="L10" s="1" t="inlineStr"/>
@@ -1082,7 +1078,7 @@
       </c>
       <c r="O10" s="1" t="inlineStr">
         <is>
-          <t>L49: isolated marker/symbol line :: 54</t>
+          <t>L47: isolated marker/symbol line :: 54</t>
         </is>
       </c>
       <c r="P10" s="1" t="inlineStr"/>
@@ -1109,7 +1105,7 @@
       </c>
       <c r="C11" s="1" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D11" s="1" t="inlineStr"/>
@@ -1121,19 +1117,19 @@
       <c r="J11" s="1" t="inlineStr"/>
       <c r="K11" s="1" t="inlineStr">
         <is>
-          <t>L104: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN | isolated marker/symbol line :: â€¢</t>
+          <t>L110: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | isolated marker/symbol line :: •</t>
         </is>
       </c>
       <c r="L11" s="1" t="inlineStr"/>
       <c r="M11" s="1" t="inlineStr"/>
       <c r="N11" s="1" t="inlineStr">
         <is>
-          <t>L42: isolated marker/symbol line :: 54</t>
+          <t>L27: stray/suspicious non-ASCII glyph(s): U+4E0A CJK UNIFIED IDEOGRAPH-4E0A | isolated marker/symbol line :: 上</t>
         </is>
       </c>
       <c r="O11" s="1" t="inlineStr">
         <is>
-          <t>L53: isolated marker/symbol line :: 64</t>
+          <t>L49: isolated marker/symbol line :: 54</t>
         </is>
       </c>
       <c r="P11" s="1" t="inlineStr"/>
@@ -1155,12 +1151,12 @@
       </c>
       <c r="B12" s="1" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>33</t>
         </is>
       </c>
       <c r="C12" s="1" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>36</t>
         </is>
       </c>
       <c r="D12" s="1" t="inlineStr"/>
@@ -1172,19 +1168,19 @@
       <c r="J12" s="1" t="inlineStr"/>
       <c r="K12" s="1" t="inlineStr">
         <is>
-          <t>L105: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN | isolated marker/symbol line :: â€¢</t>
+          <t>L114: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | isolated marker/symbol line :: •</t>
         </is>
       </c>
       <c r="L12" s="1" t="inlineStr"/>
       <c r="M12" s="1" t="inlineStr"/>
       <c r="N12" s="1" t="inlineStr">
         <is>
-          <t>L46: stray/suspicious non-ASCII glyph(s): U+00B8 CEDILLA, U+20AC EURO SIGN | isolated marker/symbol line :: ä¸€</t>
+          <t>L42: isolated marker/symbol line :: 54</t>
         </is>
       </c>
       <c r="O12" s="1" t="inlineStr">
         <is>
-          <t>L59: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN | isolated marker/symbol line :: â€¢</t>
+          <t>L53: isolated marker/symbol line :: 64</t>
         </is>
       </c>
       <c r="P12" s="1" t="inlineStr"/>
@@ -1223,19 +1219,19 @@
       <c r="J13" s="1" t="inlineStr"/>
       <c r="K13" s="1" t="inlineStr">
         <is>
-          <t>L106: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN | isolated marker/symbol line :: â€¢</t>
+          <t>L145: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | isolated marker/symbol line :: •</t>
         </is>
       </c>
       <c r="L13" s="1" t="inlineStr"/>
       <c r="M13" s="1" t="inlineStr"/>
       <c r="N13" s="1" t="inlineStr">
         <is>
-          <t>L47: isolated marker/symbol line :: 4</t>
+          <t>L46: stray/suspicious non-ASCII glyph(s): U+4E00 CJK UNIFIED IDEOGRAPH-4E00 | isolated marker/symbol line :: 一</t>
         </is>
       </c>
       <c r="O13" s="1" t="inlineStr">
         <is>
-          <t>L63: isolated marker/symbol line :: ]</t>
+          <t>L55: symbol-only separator/garbage line :: 54—55</t>
         </is>
       </c>
       <c r="P13" s="1" t="inlineStr"/>
@@ -1262,7 +1258,7 @@
       </c>
       <c r="C14" s="1" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D14" s="1" t="inlineStr"/>
@@ -1274,19 +1270,19 @@
       <c r="J14" s="1" t="inlineStr"/>
       <c r="K14" s="1" t="inlineStr">
         <is>
-          <t>L110: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN | isolated marker/symbol line :: â€¢</t>
+          <t>L147: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | isolated marker/symbol line :: •</t>
         </is>
       </c>
       <c r="L14" s="1" t="inlineStr"/>
       <c r="M14" s="1" t="inlineStr"/>
       <c r="N14" s="1" t="inlineStr">
         <is>
-          <t>L48: isolated marker/symbol line :: 64</t>
+          <t>L47: isolated marker/symbol line :: 4</t>
         </is>
       </c>
       <c r="O14" s="1" t="inlineStr">
         <is>
-          <t>L67: isolated marker/symbol line :: 60</t>
+          <t>L57: symbol-only separator/garbage line :: 55—56—57</t>
         </is>
       </c>
       <c r="P14" s="1" t="inlineStr"/>
@@ -1323,21 +1319,17 @@
       <c r="H15" s="1" t="inlineStr"/>
       <c r="I15" s="1" t="inlineStr"/>
       <c r="J15" s="1" t="inlineStr"/>
-      <c r="K15" s="1" t="inlineStr">
-        <is>
-          <t>L114: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN | isolated marker/symbol line :: â€¢</t>
-        </is>
-      </c>
+      <c r="K15" s="1" t="inlineStr"/>
       <c r="L15" s="1" t="inlineStr"/>
       <c r="M15" s="1" t="inlineStr"/>
       <c r="N15" s="1" t="inlineStr">
         <is>
-          <t>L49: isolated marker/symbol line :: d,</t>
+          <t>L48: isolated marker/symbol line :: 64</t>
         </is>
       </c>
       <c r="O15" s="1" t="inlineStr">
         <is>
-          <t>L69: isolated marker/symbol line :: 63</t>
+          <t>L59: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | isolated marker/symbol line :: •</t>
         </is>
       </c>
       <c r="P15" s="1" t="inlineStr"/>
@@ -1374,21 +1366,17 @@
       <c r="H16" s="1" t="inlineStr"/>
       <c r="I16" s="1" t="inlineStr"/>
       <c r="J16" s="1" t="inlineStr"/>
-      <c r="K16" s="1" t="inlineStr">
-        <is>
-          <t>L130: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: 107â€”108</t>
-        </is>
-      </c>
+      <c r="K16" s="1" t="inlineStr"/>
       <c r="L16" s="1" t="inlineStr"/>
       <c r="M16" s="1" t="inlineStr"/>
       <c r="N16" s="1" t="inlineStr">
         <is>
-          <t>L51: symbol-only separator/garbage line :: 55-56-57</t>
+          <t>L49: isolated marker/symbol line :: d,</t>
         </is>
       </c>
       <c r="O16" s="1" t="inlineStr">
         <is>
-          <t>L71: isolated marker/symbol line :: 58</t>
+          <t>L63: isolated marker/symbol line :: ]</t>
         </is>
       </c>
       <c r="P16" s="1" t="inlineStr"/>
@@ -1425,21 +1413,17 @@
       <c r="H17" s="1" t="inlineStr"/>
       <c r="I17" s="1" t="inlineStr"/>
       <c r="J17" s="1" t="inlineStr"/>
-      <c r="K17" s="1" t="inlineStr">
-        <is>
-          <t>L145: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN | isolated marker/symbol line :: â€¢</t>
-        </is>
-      </c>
+      <c r="K17" s="1" t="inlineStr"/>
       <c r="L17" s="1" t="inlineStr"/>
       <c r="M17" s="1" t="inlineStr"/>
       <c r="N17" s="1" t="inlineStr">
         <is>
-          <t>L53: symbol-only separator/garbage line :: 57-58</t>
+          <t>L50: symbol-only separator/garbage line :: 54 — 55</t>
         </is>
       </c>
       <c r="O17" s="1" t="inlineStr">
         <is>
-          <t>L77: isolated marker/symbol line :: 61</t>
+          <t>L65: symbol-only separator/garbage line :: 57—58</t>
         </is>
       </c>
       <c r="P17" s="1" t="inlineStr"/>
@@ -1464,21 +1448,17 @@
       <c r="H18" s="1" t="inlineStr"/>
       <c r="I18" s="1" t="inlineStr"/>
       <c r="J18" s="1" t="inlineStr"/>
-      <c r="K18" s="1" t="inlineStr">
-        <is>
-          <t>L147: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN | isolated marker/symbol line :: â€¢</t>
-        </is>
-      </c>
+      <c r="K18" s="1" t="inlineStr"/>
       <c r="L18" s="1" t="inlineStr"/>
       <c r="M18" s="1" t="inlineStr"/>
       <c r="N18" s="1" t="inlineStr">
         <is>
-          <t>L54: isolated marker/symbol line :: .</t>
+          <t>L51: symbol-only separator/garbage line :: 55-56-57</t>
         </is>
       </c>
       <c r="O18" s="1" t="inlineStr">
         <is>
-          <t>L78: symbol-only separator/garbage line :: .62</t>
+          <t>L67: isolated marker/symbol line :: 60</t>
         </is>
       </c>
       <c r="P18" s="1" t="inlineStr"/>
@@ -1503,21 +1483,17 @@
       <c r="H19" s="1" t="inlineStr"/>
       <c r="I19" s="1" t="inlineStr"/>
       <c r="J19" s="1" t="inlineStr"/>
-      <c r="K19" s="1" t="inlineStr">
-        <is>
-          <t>L149: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: Question as to the Jurisdiction of the Court of Chancery 8â€”9</t>
-        </is>
-      </c>
+      <c r="K19" s="1" t="inlineStr"/>
       <c r="L19" s="1" t="inlineStr"/>
       <c r="M19" s="1" t="inlineStr"/>
       <c r="N19" s="1" t="inlineStr">
         <is>
-          <t>L55: isolated marker/symbol line :: 0</t>
+          <t>L53: symbol-only separator/garbage line :: 57-58</t>
         </is>
       </c>
       <c r="O19" s="1" t="inlineStr">
         <is>
-          <t>L80: isolated marker/symbol line :: 62</t>
+          <t>L69: isolated marker/symbol line :: 63</t>
         </is>
       </c>
       <c r="P19" s="1" t="inlineStr"/>
@@ -1547,12 +1523,12 @@
       <c r="M20" s="1" t="inlineStr"/>
       <c r="N20" s="1" t="inlineStr">
         <is>
-          <t>L56: isolated marker/symbol line :: 60</t>
+          <t>L54: isolated marker/symbol line :: .</t>
         </is>
       </c>
       <c r="O20" s="1" t="inlineStr">
         <is>
-          <t>L82: isolated marker/symbol line :: 62</t>
+          <t>L71: isolated marker/symbol line :: 58</t>
         </is>
       </c>
       <c r="P20" s="1" t="inlineStr"/>
@@ -1582,12 +1558,12 @@
       <c r="M21" s="1" t="inlineStr"/>
       <c r="N21" s="1" t="inlineStr">
         <is>
-          <t>L57: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN | isolated marker/symbol line :: â€¢</t>
+          <t>L55: isolated marker/symbol line :: 0</t>
         </is>
       </c>
       <c r="O21" s="1" t="inlineStr">
         <is>
-          <t>L98: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN | isolated marker/symbol line :: â€¢</t>
+          <t>L73: symbol-only separator/garbage line :: 58—59</t>
         </is>
       </c>
       <c r="P21" s="1" t="inlineStr"/>
@@ -1617,12 +1593,12 @@
       <c r="M22" s="1" t="inlineStr"/>
       <c r="N22" s="1" t="inlineStr">
         <is>
-          <t>L58: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN | isolated marker/symbol line :: â€¢</t>
+          <t>L56: isolated marker/symbol line :: 60</t>
         </is>
       </c>
       <c r="O22" s="1" t="inlineStr">
         <is>
-          <t>L102: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN | isolated marker/symbol line :: â€¢</t>
+          <t>L77: isolated marker/symbol line :: 61</t>
         </is>
       </c>
       <c r="P22" s="1" t="inlineStr"/>
@@ -1652,12 +1628,12 @@
       <c r="M23" s="1" t="inlineStr"/>
       <c r="N23" s="1" t="inlineStr">
         <is>
-          <t>L59: isolated marker/symbol line :: 63</t>
+          <t>L57: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | isolated marker/symbol line :: •</t>
         </is>
       </c>
       <c r="O23" s="1" t="inlineStr">
         <is>
-          <t>L104: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN | isolated marker/symbol line :: â€¢</t>
+          <t>L78: symbol-only separator/garbage line :: .62</t>
         </is>
       </c>
       <c r="P23" s="1" t="inlineStr"/>
@@ -1687,12 +1663,12 @@
       <c r="M24" s="1" t="inlineStr"/>
       <c r="N24" s="1" t="inlineStr">
         <is>
-          <t>L61: isolated marker/symbol line :: 58</t>
+          <t>L58: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | isolated marker/symbol line :: •</t>
         </is>
       </c>
       <c r="O24" s="1" t="inlineStr">
         <is>
-          <t>L105: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN | isolated marker/symbol line :: â€¢</t>
+          <t>L80: isolated marker/symbol line :: 62</t>
         </is>
       </c>
       <c r="P24" s="1" t="inlineStr"/>
@@ -1722,12 +1698,12 @@
       <c r="M25" s="1" t="inlineStr"/>
       <c r="N25" s="1" t="inlineStr">
         <is>
-          <t>L64: isolated marker/symbol line :: 61</t>
+          <t>L59: isolated marker/symbol line :: 63</t>
         </is>
       </c>
       <c r="O25" s="1" t="inlineStr">
         <is>
-          <t>L106: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN | isolated marker/symbol line :: â€¢</t>
+          <t>L82: isolated marker/symbol line :: 62</t>
         </is>
       </c>
       <c r="P25" s="1" t="inlineStr"/>
@@ -1757,12 +1733,12 @@
       <c r="M26" s="1" t="inlineStr"/>
       <c r="N26" s="1" t="inlineStr">
         <is>
-          <t>L81: isolated marker/symbol line :: 62</t>
+          <t>L61: isolated marker/symbol line :: 58</t>
         </is>
       </c>
       <c r="O26" s="1" t="inlineStr">
         <is>
-          <t>L110: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN | isolated marker/symbol line :: â€¢</t>
+          <t>L98: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | isolated marker/symbol line :: •</t>
         </is>
       </c>
       <c r="P26" s="1" t="inlineStr"/>
@@ -1792,12 +1768,12 @@
       <c r="M27" s="1" t="inlineStr"/>
       <c r="N27" s="1" t="inlineStr">
         <is>
-          <t>L82: isolated marker/symbol line :: 62</t>
+          <t>L62: symbol-only separator/garbage line :: 58 — 59</t>
         </is>
       </c>
       <c r="O27" s="1" t="inlineStr">
         <is>
-          <t>L114: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN | isolated marker/symbol line :: â€¢</t>
+          <t>L102: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | isolated marker/symbol line :: •</t>
         </is>
       </c>
       <c r="P27" s="1" t="inlineStr"/>
@@ -1827,12 +1803,12 @@
       <c r="M28" s="1" t="inlineStr"/>
       <c r="N28" s="1" t="inlineStr">
         <is>
-          <t>L84: isolated marker/symbol line :: 62</t>
+          <t>L64: isolated marker/symbol line :: 61</t>
         </is>
       </c>
       <c r="O28" s="1" t="inlineStr">
         <is>
-          <t>L138: isolated marker/symbol line :: 8</t>
+          <t>L104: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | isolated marker/symbol line :: •</t>
         </is>
       </c>
       <c r="P28" s="1" t="inlineStr"/>
@@ -1862,12 +1838,12 @@
       <c r="M29" s="1" t="inlineStr"/>
       <c r="N29" s="1" t="inlineStr">
         <is>
-          <t>L89: isolated marker/symbol line :: 8</t>
+          <t>L81: isolated marker/symbol line :: 62</t>
         </is>
       </c>
       <c r="O29" s="1" t="inlineStr">
         <is>
-          <t>L140: isolated marker/symbol line :: 8</t>
+          <t>L105: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | isolated marker/symbol line :: •</t>
         </is>
       </c>
       <c r="P29" s="1" t="inlineStr"/>
@@ -1897,12 +1873,12 @@
       <c r="M30" s="1" t="inlineStr"/>
       <c r="N30" s="1" t="inlineStr">
         <is>
-          <t>L90: isolated marker/symbol line :: 8</t>
+          <t>L82: isolated marker/symbol line :: 62</t>
         </is>
       </c>
       <c r="O30" s="1" t="inlineStr">
         <is>
-          <t>L145: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN | isolated marker/symbol line :: â€¢</t>
+          <t>L106: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | isolated marker/symbol line :: •</t>
         </is>
       </c>
       <c r="P30" s="1" t="inlineStr"/>
@@ -1930,10 +1906,14 @@
       <c r="K31" s="1" t="inlineStr"/>
       <c r="L31" s="1" t="inlineStr"/>
       <c r="M31" s="1" t="inlineStr"/>
-      <c r="N31" s="1" t="inlineStr"/>
+      <c r="N31" s="1" t="inlineStr">
+        <is>
+          <t>L84: isolated marker/symbol line :: 62</t>
+        </is>
+      </c>
       <c r="O31" s="1" t="inlineStr">
         <is>
-          <t>L147: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN | isolated marker/symbol line :: â€¢</t>
+          <t>L110: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | isolated marker/symbol line :: •</t>
         </is>
       </c>
       <c r="P31" s="1" t="inlineStr"/>
@@ -1947,6 +1927,204 @@
       <c r="X31" s="1" t="inlineStr"/>
       <c r="Y31" s="1" t="inlineStr"/>
     </row>
+    <row r="32">
+      <c r="A32" s="1" t="inlineStr"/>
+      <c r="B32" s="1" t="inlineStr"/>
+      <c r="C32" s="1" t="inlineStr"/>
+      <c r="D32" s="1" t="inlineStr"/>
+      <c r="E32" s="1" t="inlineStr"/>
+      <c r="F32" s="1" t="inlineStr"/>
+      <c r="G32" s="1" t="inlineStr"/>
+      <c r="H32" s="1" t="inlineStr"/>
+      <c r="I32" s="1" t="inlineStr"/>
+      <c r="J32" s="1" t="inlineStr"/>
+      <c r="K32" s="1" t="inlineStr"/>
+      <c r="L32" s="1" t="inlineStr"/>
+      <c r="M32" s="1" t="inlineStr"/>
+      <c r="N32" s="1" t="inlineStr">
+        <is>
+          <t>L86: symbol-only separator/garbage line :: 107 — 108</t>
+        </is>
+      </c>
+      <c r="O32" s="1" t="inlineStr">
+        <is>
+          <t>L114: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | isolated marker/symbol line :: •</t>
+        </is>
+      </c>
+      <c r="P32" s="1" t="inlineStr"/>
+      <c r="Q32" s="1" t="inlineStr"/>
+      <c r="R32" s="1" t="inlineStr"/>
+      <c r="S32" s="1" t="inlineStr"/>
+      <c r="T32" s="1" t="inlineStr"/>
+      <c r="U32" s="1" t="inlineStr"/>
+      <c r="V32" s="1" t="inlineStr"/>
+      <c r="W32" s="1" t="inlineStr"/>
+      <c r="X32" s="1" t="inlineStr"/>
+      <c r="Y32" s="1" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="1" t="inlineStr"/>
+      <c r="B33" s="1" t="inlineStr"/>
+      <c r="C33" s="1" t="inlineStr"/>
+      <c r="D33" s="1" t="inlineStr"/>
+      <c r="E33" s="1" t="inlineStr"/>
+      <c r="F33" s="1" t="inlineStr"/>
+      <c r="G33" s="1" t="inlineStr"/>
+      <c r="H33" s="1" t="inlineStr"/>
+      <c r="I33" s="1" t="inlineStr"/>
+      <c r="J33" s="1" t="inlineStr"/>
+      <c r="K33" s="1" t="inlineStr"/>
+      <c r="L33" s="1" t="inlineStr"/>
+      <c r="M33" s="1" t="inlineStr"/>
+      <c r="N33" s="1" t="inlineStr">
+        <is>
+          <t>L89: isolated marker/symbol line :: 8</t>
+        </is>
+      </c>
+      <c r="O33" s="1" t="inlineStr">
+        <is>
+          <t>L130: symbol-only separator/garbage line :: 107—108</t>
+        </is>
+      </c>
+      <c r="P33" s="1" t="inlineStr"/>
+      <c r="Q33" s="1" t="inlineStr"/>
+      <c r="R33" s="1" t="inlineStr"/>
+      <c r="S33" s="1" t="inlineStr"/>
+      <c r="T33" s="1" t="inlineStr"/>
+      <c r="U33" s="1" t="inlineStr"/>
+      <c r="V33" s="1" t="inlineStr"/>
+      <c r="W33" s="1" t="inlineStr"/>
+      <c r="X33" s="1" t="inlineStr"/>
+      <c r="Y33" s="1" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="1" t="inlineStr"/>
+      <c r="B34" s="1" t="inlineStr"/>
+      <c r="C34" s="1" t="inlineStr"/>
+      <c r="D34" s="1" t="inlineStr"/>
+      <c r="E34" s="1" t="inlineStr"/>
+      <c r="F34" s="1" t="inlineStr"/>
+      <c r="G34" s="1" t="inlineStr"/>
+      <c r="H34" s="1" t="inlineStr"/>
+      <c r="I34" s="1" t="inlineStr"/>
+      <c r="J34" s="1" t="inlineStr"/>
+      <c r="K34" s="1" t="inlineStr"/>
+      <c r="L34" s="1" t="inlineStr"/>
+      <c r="M34" s="1" t="inlineStr"/>
+      <c r="N34" s="1" t="inlineStr">
+        <is>
+          <t>L90: isolated marker/symbol line :: 8</t>
+        </is>
+      </c>
+      <c r="O34" s="1" t="inlineStr">
+        <is>
+          <t>L138: isolated marker/symbol line :: 8</t>
+        </is>
+      </c>
+      <c r="P34" s="1" t="inlineStr"/>
+      <c r="Q34" s="1" t="inlineStr"/>
+      <c r="R34" s="1" t="inlineStr"/>
+      <c r="S34" s="1" t="inlineStr"/>
+      <c r="T34" s="1" t="inlineStr"/>
+      <c r="U34" s="1" t="inlineStr"/>
+      <c r="V34" s="1" t="inlineStr"/>
+      <c r="W34" s="1" t="inlineStr"/>
+      <c r="X34" s="1" t="inlineStr"/>
+      <c r="Y34" s="1" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="1" t="inlineStr"/>
+      <c r="B35" s="1" t="inlineStr"/>
+      <c r="C35" s="1" t="inlineStr"/>
+      <c r="D35" s="1" t="inlineStr"/>
+      <c r="E35" s="1" t="inlineStr"/>
+      <c r="F35" s="1" t="inlineStr"/>
+      <c r="G35" s="1" t="inlineStr"/>
+      <c r="H35" s="1" t="inlineStr"/>
+      <c r="I35" s="1" t="inlineStr"/>
+      <c r="J35" s="1" t="inlineStr"/>
+      <c r="K35" s="1" t="inlineStr"/>
+      <c r="L35" s="1" t="inlineStr"/>
+      <c r="M35" s="1" t="inlineStr"/>
+      <c r="N35" s="1" t="inlineStr"/>
+      <c r="O35" s="1" t="inlineStr">
+        <is>
+          <t>L140: isolated marker/symbol line :: 8</t>
+        </is>
+      </c>
+      <c r="P35" s="1" t="inlineStr"/>
+      <c r="Q35" s="1" t="inlineStr"/>
+      <c r="R35" s="1" t="inlineStr"/>
+      <c r="S35" s="1" t="inlineStr"/>
+      <c r="T35" s="1" t="inlineStr"/>
+      <c r="U35" s="1" t="inlineStr"/>
+      <c r="V35" s="1" t="inlineStr"/>
+      <c r="W35" s="1" t="inlineStr"/>
+      <c r="X35" s="1" t="inlineStr"/>
+      <c r="Y35" s="1" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="1" t="inlineStr"/>
+      <c r="B36" s="1" t="inlineStr"/>
+      <c r="C36" s="1" t="inlineStr"/>
+      <c r="D36" s="1" t="inlineStr"/>
+      <c r="E36" s="1" t="inlineStr"/>
+      <c r="F36" s="1" t="inlineStr"/>
+      <c r="G36" s="1" t="inlineStr"/>
+      <c r="H36" s="1" t="inlineStr"/>
+      <c r="I36" s="1" t="inlineStr"/>
+      <c r="J36" s="1" t="inlineStr"/>
+      <c r="K36" s="1" t="inlineStr"/>
+      <c r="L36" s="1" t="inlineStr"/>
+      <c r="M36" s="1" t="inlineStr"/>
+      <c r="N36" s="1" t="inlineStr"/>
+      <c r="O36" s="1" t="inlineStr">
+        <is>
+          <t>L145: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | isolated marker/symbol line :: •</t>
+        </is>
+      </c>
+      <c r="P36" s="1" t="inlineStr"/>
+      <c r="Q36" s="1" t="inlineStr"/>
+      <c r="R36" s="1" t="inlineStr"/>
+      <c r="S36" s="1" t="inlineStr"/>
+      <c r="T36" s="1" t="inlineStr"/>
+      <c r="U36" s="1" t="inlineStr"/>
+      <c r="V36" s="1" t="inlineStr"/>
+      <c r="W36" s="1" t="inlineStr"/>
+      <c r="X36" s="1" t="inlineStr"/>
+      <c r="Y36" s="1" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="1" t="inlineStr"/>
+      <c r="B37" s="1" t="inlineStr"/>
+      <c r="C37" s="1" t="inlineStr"/>
+      <c r="D37" s="1" t="inlineStr"/>
+      <c r="E37" s="1" t="inlineStr"/>
+      <c r="F37" s="1" t="inlineStr"/>
+      <c r="G37" s="1" t="inlineStr"/>
+      <c r="H37" s="1" t="inlineStr"/>
+      <c r="I37" s="1" t="inlineStr"/>
+      <c r="J37" s="1" t="inlineStr"/>
+      <c r="K37" s="1" t="inlineStr"/>
+      <c r="L37" s="1" t="inlineStr"/>
+      <c r="M37" s="1" t="inlineStr"/>
+      <c r="N37" s="1" t="inlineStr"/>
+      <c r="O37" s="1" t="inlineStr">
+        <is>
+          <t>L147: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | isolated marker/symbol line :: •</t>
+        </is>
+      </c>
+      <c r="P37" s="1" t="inlineStr"/>
+      <c r="Q37" s="1" t="inlineStr"/>
+      <c r="R37" s="1" t="inlineStr"/>
+      <c r="S37" s="1" t="inlineStr"/>
+      <c r="T37" s="1" t="inlineStr"/>
+      <c r="U37" s="1" t="inlineStr"/>
+      <c r="V37" s="1" t="inlineStr"/>
+      <c r="W37" s="1" t="inlineStr"/>
+      <c r="X37" s="1" t="inlineStr"/>
+      <c r="Y37" s="1" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
